--- a/Bin/A-QIP-WS001-06C.xlsx
+++ b/Bin/A-QIP-WS001-06C.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ERP SOURCE CODE\Bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A50310-7793-4D80-9DF5-67AFFDCD51D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="12240"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QIP VII 04 01  " sheetId="1" r:id="rId1"/>
@@ -433,9 +434,6 @@
     <t xml:space="preserve">Tổng cộng /总共/ Total </t>
   </si>
   <si>
-    <t>OK/NG</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">NHÃN HIỆU </t>
     </r>
@@ -458,18 +456,44 @@
       </rPr>
       <t>: 
 Brand name:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kết quả
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>結果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Result</t>
     </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -622,6 +646,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -713,49 +744,49 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="17">
-    <cellStyle name="Comma 2" xfId="2"/>
-    <cellStyle name="Comma 4 2" xfId="3"/>
-    <cellStyle name="Excel Built-in Normal" xfId="4"/>
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Comma 4 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 2 2" xfId="5"/>
-    <cellStyle name="Normal 2 3" xfId="6"/>
-    <cellStyle name="Normal 3" xfId="7"/>
-    <cellStyle name="Normal 4" xfId="8"/>
-    <cellStyle name="Normal 5" xfId="9"/>
-    <cellStyle name="Normal 6" xfId="10"/>
-    <cellStyle name="Normal 6 2" xfId="11"/>
-    <cellStyle name="Normal 7" xfId="12"/>
-    <cellStyle name="Normal 8" xfId="13"/>
-    <cellStyle name="Normal 9" xfId="14"/>
-    <cellStyle name="Percent 4 2" xfId="15"/>
-    <cellStyle name="Style 1" xfId="16"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 5" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 6" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 6 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 7" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 8" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 9" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Percent 4 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Style 1" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -996,7 +1027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1015,36 +1046,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="72" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" s="2" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="15" t="s">
+      <c r="A2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="76.5">
       <c r="A3" s="7" t="s">
@@ -1077,8 +1108,8 @@
       <c r="J3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>17</v>
+      <c r="K3" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="27" customHeight="1">
@@ -1094,106 +1125,106 @@
       <c r="J4" s="7"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" s="12" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:11" s="11" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="48" customHeight="1">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16" t="s">
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" s="6" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
